--- a/data/trans_orig/IP25A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP25A-Edad-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3398</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>3049</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>3966</t>
+          <t>3671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>569</t>
+          <t>560</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5336</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>18803</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29800</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16026</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>28107</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37780</t>
+          <t>37327</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54500</t>
+          <t>54331</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22223</t>
+          <t>21450</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33306</t>
+          <t>33300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27209</t>
+          <t>26994</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39069</t>
+          <t>39304</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>70,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53111</t>
+          <t>52815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>69286</t>
+          <t>69500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2217</t>
+          <t>1835</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10081</t>
+          <t>9991</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>16902</t>
+          <t>16435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10642</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23988</t>
+          <t>24139</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>46814</t>
+          <t>47422</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>69266</t>
+          <t>69840</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,47 +1430,47 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>19,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>28,33%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>55670</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>46038</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>66981</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>18,99%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>28,1%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>55670</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>45944</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>65983</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>22,96%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>18,95%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98959</t>
+          <t>97749</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130755</t>
+          <t>129209</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,24%</t>
+          <t>19,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,43%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133876</t>
+          <t>132515</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158963</t>
+          <t>157717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>64,49%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>128104</t>
+          <t>127582</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>153378</t>
+          <t>151311</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>266815</t>
+          <t>268841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>302917</t>
+          <t>303979</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,95%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29007</t>
+          <t>28804</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47214</t>
+          <t>46727</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>27203</t>
+          <t>27879</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45744</t>
+          <t>45277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>62734</t>
+          <t>61997</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>88475</t>
+          <t>86602</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,09%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5782</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15583</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,49 +1886,49 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>10799</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6532</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>16724</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>8,02%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>12,42%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>10799</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>6389</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16849</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>30</t>
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>13725</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28527</t>
+          <t>27648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33574</t>
+          <t>33524</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52087</t>
+          <t>51066</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>40,7%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>47276</t>
+          <t>47405</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>65408</t>
+          <t>66689</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>48,56%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>85181</t>
+          <t>86811</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>110462</t>
+          <t>111314</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>54532</t>
+          <t>55035</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>73159</t>
+          <t>73301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52730</t>
+          <t>52849</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>71305</t>
+          <t>71537</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>53,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113103</t>
+          <t>113869</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139390</t>
+          <t>138471</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>53,23%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5269</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15318</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21871</t>
+          <t>22319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>17819</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32853</t>
+          <t>33717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>19880</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>35639</t>
+          <t>35501</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>41683</t>
+          <t>41780</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63348</t>
+          <t>63980</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>16,53%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>70709</t>
+          <t>71668</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91881</t>
+          <t>92917</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>69871</t>
+          <t>69432</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>91138</t>
+          <t>92450</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>146679</t>
+          <t>145247</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>177343</t>
+          <t>178810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>37,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>46,2%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>61348</t>
+          <t>59384</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>82172</t>
+          <t>80737</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67976</t>
+          <t>67190</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90111</t>
+          <t>89449</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>133618</t>
+          <t>134843</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>166275</t>
+          <t>165925</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,87%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>6594</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17572</t>
+          <t>17871</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7667</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19091</t>
+          <t>18630</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17269</t>
+          <t>16677</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32436</t>
+          <t>32177</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29970</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50301</t>
+          <t>51218</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38841</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60353</t>
+          <t>60232</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71130</t>
+          <t>75658</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>102545</t>
+          <t>104690</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,4%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>166951</t>
+          <t>164920</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>202876</t>
+          <t>201864</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>172916</t>
+          <t>172001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>211494</t>
+          <t>211871</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>351512</t>
+          <t>347600</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>402576</t>
+          <t>400946</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>282798</t>
+          <t>285411</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>324170</t>
+          <t>324598</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>280658</t>
+          <t>283827</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>323134</t>
+          <t>325446</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>580127</t>
+          <t>576845</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>636525</t>
+          <t>636276</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>72235</t>
+          <t>73778</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>99891</t>
+          <t>101906</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>73415</t>
+          <t>74902</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>101214</t>
+          <t>102460</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>154484</t>
+          <t>154167</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>196713</t>
+          <t>193576</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,54%</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5107</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>976</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7881</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1678</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10148</t>
+          <t>8932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1342</t>
+          <t>1377</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2801</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10125</t>
+          <t>10773</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5349</t>
+          <t>5663</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15414</t>
+          <t>15023</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>38965</t>
+          <t>38854</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30586</t>
+          <t>30249</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46201</t>
+          <t>45436</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59539</t>
+          <t>58650</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80149</t>
+          <t>79519</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,92%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,64%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>38380</t>
+          <t>39147</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>52590</t>
+          <t>52696</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>47,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33333</t>
+          <t>33240</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48554</t>
+          <t>48545</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75698</t>
+          <t>76542</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96340</t>
+          <t>97624</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7336</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18512</t>
+          <t>18710</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13176</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>28135</t>
+          <t>28162</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>23532</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>41406</t>
+          <t>42117</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52717</t>
+          <t>52168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74407</t>
+          <t>74272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>64329</t>
+          <t>65064</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89645</t>
+          <t>89678</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121985</t>
+          <t>123941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155980</t>
+          <t>157002</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,57%</t>
+          <t>31,78%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>107998</t>
+          <t>107994</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133111</t>
+          <t>133553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126668</t>
+          <t>128358</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>154628</t>
+          <t>154682</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>48,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>243466</t>
+          <t>243411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>282319</t>
+          <t>279475</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>56,56%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24186</t>
+          <t>25039</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>41421</t>
+          <t>42784</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>21389</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>38426</t>
+          <t>38389</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>49808</t>
+          <t>50665</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>75973</t>
+          <t>75923</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,37%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7872</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>19494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>10784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24635</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>22413</t>
+          <t>20452</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>39166</t>
+          <t>39520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>44783</t>
+          <t>44716</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>64697</t>
+          <t>63967</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>41,94%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>45688</t>
+          <t>45087</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>64715</t>
+          <t>63469</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>96899</t>
+          <t>94595</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>124147</t>
+          <t>120842</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>39,0%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66166</t>
+          <t>66840</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>87126</t>
+          <t>86910</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,89%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60887</t>
+          <t>61391</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81750</t>
+          <t>80864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,54%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133980</t>
+          <t>135025</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163077</t>
+          <t>164126</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,97%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6182</t>
+          <t>6039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16833</t>
+          <t>16026</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>20221</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16771</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>32529</t>
+          <t>31913</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>15624</t>
+          <t>15768</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30276</t>
+          <t>30015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15231</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29952</t>
+          <t>29377</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>34580</t>
+          <t>35565</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54737</t>
+          <t>54873</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,11%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>46242</t>
+          <t>44762</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>66398</t>
+          <t>65415</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42407</t>
+          <t>42281</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>62156</t>
+          <t>62172</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>92562</t>
+          <t>93939</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122456</t>
+          <t>121008</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>63574</t>
+          <t>62670</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>84260</t>
+          <t>84323</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>50,71%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>81023</t>
+          <t>80542</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102594</t>
+          <t>102070</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>58,85%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150933</t>
+          <t>151421</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>180984</t>
+          <t>181345</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>53,24%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10149</t>
+          <t>10041</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22727</t>
+          <t>22445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5516</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14810</t>
+          <t>15846</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17720</t>
+          <t>17510</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33208</t>
+          <t>33837</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,93%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>37854</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>59229</t>
+          <t>60591</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>48835</t>
+          <t>48529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>73639</t>
+          <t>75443</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>93248</t>
+          <t>93628</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>124665</t>
+          <t>127224</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>157589</t>
+          <t>158906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>197938</t>
+          <t>195581</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>170188</t>
+          <t>170053</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>208475</t>
+          <t>208719</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>337908</t>
+          <t>337242</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>391112</t>
+          <t>390808</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,72%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>282950</t>
+          <t>282209</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>324299</t>
+          <t>323836</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>321184</t>
+          <t>321945</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>365214</t>
+          <t>363940</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>613462</t>
+          <t>617652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>674818</t>
+          <t>676720</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>89695</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>118900</t>
+          <t>120209</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>77980</t>
+          <t>78276</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>106742</t>
+          <t>109641</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>176823</t>
+          <t>174682</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>218760</t>
+          <t>220870</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,8%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8769</t>
+          <t>8927</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3127</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2277</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9540</t>
+          <t>10398</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4127</t>
+          <t>4259</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12085</t>
+          <t>11603</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9188</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19888</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15647</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28598</t>
+          <t>28636</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,25%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>26991</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40442</t>
+          <t>40245</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,27%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29270</t>
+          <t>29798</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>43529</t>
+          <t>43863</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>59497</t>
+          <t>60963</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79787</t>
+          <t>79472</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,42%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20522</t>
+          <t>20747</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32897</t>
+          <t>34044</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19341</t>
+          <t>19465</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32581</t>
+          <t>32526</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42226</t>
+          <t>41936</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61327</t>
+          <t>60998</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10262</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>22335</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18028</t>
+          <t>17514</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>34180</t>
+          <t>32819</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>30946</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>50264</t>
+          <t>50567</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>62854</t>
+          <t>62412</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>84089</t>
+          <t>83485</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>71379</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97610</t>
+          <t>96382</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>28,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140118</t>
+          <t>139182</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171032</t>
+          <t>172107</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,42%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76262</t>
+          <t>76848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98904</t>
+          <t>99623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99936</t>
+          <t>101551</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>125520</t>
+          <t>126895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183836</t>
+          <t>186267</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>218918</t>
+          <t>220164</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,14%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>31428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>18907</t>
+          <t>18885</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34395</t>
+          <t>34690</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39423</t>
+          <t>40091</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60460</t>
+          <t>62311</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>14588</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>29250</t>
+          <t>28968</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>17481</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>32115</t>
+          <t>31958</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>34957</t>
+          <t>35174</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>55495</t>
+          <t>56036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,17%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49334</t>
+          <t>50262</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>70502</t>
+          <t>70980</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58256</t>
+          <t>58944</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>80010</t>
+          <t>80782</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>115142</t>
+          <t>113333</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144913</t>
+          <t>143930</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>30,68%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,96%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>66834</t>
+          <t>67895</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>88691</t>
+          <t>90286</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,48%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59981</t>
+          <t>59315</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>81344</t>
+          <t>82234</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>133286</t>
+          <t>132754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163590</t>
+          <t>165855</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17074</t>
+          <t>17238</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33107</t>
+          <t>32458</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15404</t>
+          <t>15866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30133</t>
+          <t>30144</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36180</t>
+          <t>36996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58675</t>
+          <t>57027</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22669</t>
+          <t>22203</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>38423</t>
+          <t>39047</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15943</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29883</t>
+          <t>30665</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40817</t>
+          <t>41760</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62802</t>
+          <t>64600</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>57815</t>
+          <t>58491</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>79710</t>
+          <t>79593</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>35,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>47,79%</t>
+          <t>47,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>57684</t>
+          <t>56692</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78194</t>
+          <t>78660</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,48%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122968</t>
+          <t>121927</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>152659</t>
+          <t>153063</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>46,21%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42770</t>
+          <t>42857</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>64013</t>
+          <t>63767</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>54346</t>
+          <t>53932</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>75220</t>
+          <t>75152</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>104186</t>
+          <t>103023</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>133935</t>
+          <t>131671</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>39,75%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>10080</t>
+          <t>10007</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22658</t>
+          <t>21994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>15680</t>
+          <t>16842</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18290</t>
+          <t>18108</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34197</t>
+          <t>34373</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>58241</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>85717</t>
+          <t>85247</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>59086</t>
+          <t>58603</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>86155</t>
+          <t>86721</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>123066</t>
+          <t>124589</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>162683</t>
+          <t>160649</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>188833</t>
+          <t>191259</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>227249</t>
+          <t>228033</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>215024</t>
+          <t>215317</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>254255</t>
+          <t>256362</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>414361</t>
+          <t>417968</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>471036</t>
+          <t>472738</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>233220</t>
+          <t>233266</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>272039</t>
+          <t>272241</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>263962</t>
+          <t>262142</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>305403</t>
+          <t>305591</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>509038</t>
+          <t>507451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>566359</t>
+          <t>564289</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>77686</t>
+          <t>77355</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>104903</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>70086</t>
+          <t>70337</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>98611</t>
+          <t>97781</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>153922</t>
+          <t>154429</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>194687</t>
+          <t>194649</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3819</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9984,7 +9984,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10039,7 +10039,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5103</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1501</t>
+          <t>1464</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7167</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2153</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4889</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13759</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>11,54%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9614</t>
+          <t>9095</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>19609</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>14681</t>
+          <t>14727</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25280</t>
+          <t>25778</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>26652</t>
+          <t>25883</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>41847</t>
+          <t>41078</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>35,48%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32311</t>
+          <t>31830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>42774</t>
+          <t>42203</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>56,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29180</t>
+          <t>29302</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>40842</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>63747</t>
+          <t>64462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>79696</t>
+          <t>80677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,83%</t>
+          <t>69,67%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3499</t>
+          <t>3695</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2334</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>11167</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7538</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>19288</t>
+          <t>18883</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>7750</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>18861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13796</t>
+          <t>13772</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28207</t>
+          <t>29055</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>24328</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>43055</t>
+          <t>43829</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>66144</t>
+          <t>67543</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>87066</t>
+          <t>87766</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,57%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76140</t>
+          <t>75678</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99089</t>
+          <t>98963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147855</t>
+          <t>146631</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178956</t>
+          <t>178929</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,75%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,95%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>49363</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69284</t>
+          <t>69092</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,47%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57960</t>
+          <t>58845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80159</t>
+          <t>80012</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10922,12 +10922,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>113475</t>
+          <t>114363</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>142964</t>
+          <t>142135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>33,58%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,06%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2740</t>
+          <t>2917</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19242</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9103</t>
+          <t>8954</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11157,7 +11157,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5798</t>
+          <t>6357</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>24176</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,28%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>17634</t>
+          <t>17622</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>37087</t>
+          <t>37310</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11235,7 +11235,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>19114</t>
+          <t>20075</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>38299</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>40154</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70077</t>
+          <t>68184</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69452</t>
+          <t>69760</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93225</t>
+          <t>93341</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>93526</t>
+          <t>94316</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>123277</t>
+          <t>122398</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>173275</t>
+          <t>169480</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>206992</t>
+          <t>208131</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,03%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>54,09%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46863</t>
+          <t>46584</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>67986</t>
+          <t>68451</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>60045</t>
+          <t>60309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>87031</t>
+          <t>87798</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>113937</t>
+          <t>114657</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146917</t>
+          <t>149069</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,18%</t>
+          <t>38,74%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1178</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>13119</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>5329</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18284</t>
+          <t>18302</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19291</t>
+          <t>19928</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40148</t>
+          <t>40459</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>25283</t>
+          <t>25331</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48564</t>
+          <t>46939</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49818</t>
+          <t>50443</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80239</t>
+          <t>79898</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,91%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>84174</t>
+          <t>80739</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>141238</t>
+          <t>141764</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>29,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,23%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>123877</t>
+          <t>120721</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>163735</t>
+          <t>163731</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>39,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>224437</t>
+          <t>225143</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>293691</t>
+          <t>294102</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>39,07%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,2%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>94344</t>
+          <t>92983</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>166384</t>
+          <t>167399</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>34,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,52%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97604</t>
+          <t>99410</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>143142</t>
+          <t>145891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,12 +12060,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,1%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>205377</t>
+          <t>202634</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>288160</t>
+          <t>287961</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>50,13%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12536</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>32274</t>
+          <t>33047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,47 +12275,47 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
+          <t>23920</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2,07%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>34568</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
           <t>24585</t>
         </is>
       </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>1,2%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>3,24%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>34568</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>24886</t>
-        </is>
-      </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>48980</t>
+          <t>47959</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,39%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>56949</t>
+          <t>54877</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>88063</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>73126</t>
+          <t>73930</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105371</t>
+          <t>106747</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>137963</t>
+          <t>139071</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>181697</t>
+          <t>185336</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>254085</t>
+          <t>256568</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>320838</t>
+          <t>322013</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>327451</t>
+          <t>327457</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>384438</t>
+          <t>385562</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>605049</t>
+          <t>607119</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>689743</t>
+          <t>696254</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>242859</t>
+          <t>243566</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>321101</t>
+          <t>326023</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>270044</t>
+          <t>269488</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>326274</t>
+          <t>330181</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>527863</t>
+          <t>523578</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>622510</t>
+          <t>620365</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
